--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_la_araucania.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:26</t>
+    <t xml:space="preserve">2026-09-24 01:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -570,10 +570,10 @@
         <v>-0.15</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +590,13 @@
         <v>32</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="4">
@@ -607,7 +607,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>32</v>
@@ -616,10 +616,10 @@
         <v>-0.05</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="5">
@@ -639,7 +639,7 @@
         <v>0.22</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.22</v>
@@ -662,7 +662,7 @@
         <v>0.26</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>-0.33</v>
@@ -676,16 +676,16 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0.3</v>
@@ -705,13 +705,13 @@
         <v>32</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -728,10 +728,10 @@
         <v>32</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.13</v>
@@ -745,16 +745,16 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>31</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.39</v>
@@ -768,16 +768,16 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>31</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.38</v>
@@ -797,13 +797,13 @@
         <v>32</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="13">
@@ -814,19 +814,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="14">
@@ -843,13 +843,13 @@
         <v>32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="15">
@@ -860,19 +860,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
@@ -883,19 +883,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17">
@@ -912,13 +912,13 @@
         <v>32</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="18">
@@ -929,7 +929,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>32</v>
@@ -938,10 +938,10 @@
         <v>-0.41</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -961,10 +961,10 @@
         <v>-0.2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="20">
@@ -981,10 +981,10 @@
         <v>32</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.14</v>
@@ -998,7 +998,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>32</v>
@@ -1007,10 +1007,10 @@
         <v>0.06</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="22">
@@ -1027,10 +1027,10 @@
         <v>32</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.02</v>
@@ -1044,16 +1044,16 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>-0.26</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_la_araucania.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:16</t>
+    <t xml:space="preserve">2026-10-01 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_la_araucania.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:13</t>
+    <t xml:space="preserve">2026-10-05 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
